--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251228_201458.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251228_201458.xlsx
@@ -5436,7 +5436,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251228_201458.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251228_201458.xlsx
@@ -5436,7 +5436,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251228_201458.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251228_201458.xlsx
@@ -5552,7 +5552,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251228_201458.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251228_201458.xlsx
@@ -3754,7 +3754,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251228_201458.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251228_201458.xlsx
@@ -3754,7 +3754,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251228_201458.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251228_201458.xlsx
@@ -3754,7 +3754,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251228_201458.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251228_201458.xlsx
@@ -5436,7 +5436,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251228_201458.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251228_201458.xlsx
@@ -3754,7 +3754,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251228_201458.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251228_201458.xlsx
@@ -3754,7 +3754,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
